--- a/human_resources_forms/011_harassment_report_form--human_resources_forms.xlsx
+++ b/human_resources_forms/011_harassment_report_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>resolution_status1</t>
+          <t>resolution_status_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Resolution Status1</t>
+          <t>Resolution Status 1</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>resolution_status2</t>
+          <t>resolution_status_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Resolution Status2</t>
+          <t>Resolution Status 2</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>resolution_status3</t>
+          <t>resolution_status_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Resolution Status3</t>
+          <t>Resolution Status 3</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>follow-up_status1</t>
+          <t>follow-up_status_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Follow-up Status1</t>
+          <t>Follow-up Status 1</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>follow-up_status2</t>
+          <t>follow-up_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Follow-up Status2</t>
+          <t>Follow-up Status 2</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>follow-up_status3</t>
+          <t>follow-up_status_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Follow-up Status3</t>
+          <t>Follow-up Status 3</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>follow-up_status21</t>
+          <t>follow-up_status_21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Follow-up Status21</t>
+          <t>Follow-up Status 21</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>follow-up_status22</t>
+          <t>follow-up_status_22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Follow-up Status22</t>
+          <t>Follow-up Status 22</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>follow-up_status23</t>
+          <t>follow-up_status_23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Follow-up Status23</t>
+          <t>Follow-up Status 23</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>follow-up_status31</t>
+          <t>follow-up_status_31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Follow-up Status31</t>
+          <t>Follow-up Status 31</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>follow-up_status32</t>
+          <t>follow-up_status_32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Follow-up Status32</t>
+          <t>Follow-up Status 32</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>follow-up_status33</t>
+          <t>follow-up_status_33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Follow-up Status33</t>
+          <t>Follow-up Status 33</t>
         </is>
       </c>
     </row>
